--- a/docs/custos-10mil-pacientes.xlsx
+++ b/docs/custos-10mil-pacientes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="210">
   <si>
     <t>Premissas (mude aqui; o resto recalcula)</t>
   </si>
@@ -73,7 +73,7 @@
     <t>Idem.</t>
   </si>
   <si>
-    <t>Chat da Lu: mensagens por paciente por mês</t>
+    <t>Chat da Luna: mensagens por paciente por mês</t>
   </si>
   <si>
     <t>msgs</t>
@@ -82,7 +82,7 @@
     <t>Estimativa. Teto atual no backend: 60/dia e 600/mês por conta (limites.js).</t>
   </si>
   <si>
-    <t>Chat da Lu: tokens de entrada por mensagem</t>
+    <t>Chat da Luna: tokens de entrada por mensagem</t>
   </si>
   <si>
     <t>tokens</t>
@@ -91,7 +91,7 @@
     <t>Estimativa: prompt do sistema + contexto (perfil, plano, 40 receitas candidatas) + histórico.</t>
   </si>
   <si>
-    <t>Chat da Lu: tokens de saída por mensagem</t>
+    <t>Chat da Luna: tokens de saída por mensagem</t>
   </si>
   <si>
     <t>Estimativa (resposta curta em JSON).</t>
@@ -136,6 +136,27 @@
     <t>Resumo do dia: tokens de saída</t>
   </si>
   <si>
+    <t>Rascunho de resposta pra Luciana (Luna): por paciente por mês</t>
+  </si>
+  <si>
+    <t>rascunhos</t>
+  </si>
+  <si>
+    <t>Estimativa: = dúvidas por paciente por mês. Uma chamada por dúvida não clínica (services/triagem.js). Dúvida de saúde não chama IA.</t>
+  </si>
+  <si>
+    <t>Rascunho: tokens de entrada</t>
+  </si>
+  <si>
+    <t>Estimativa: prompt + perfil não clínico + plano da semana + pergunta.</t>
+  </si>
+  <si>
+    <t>Rascunho: tokens de saída</t>
+  </si>
+  <si>
+    <t>Estimativa (2 a 5 frases + motivo).</t>
+  </si>
+  <si>
     <t>Síntese do dashboard: chamadas por dia (custo global, não por paciente)</t>
   </si>
   <si>
@@ -358,7 +379,7 @@
     <t>Como foi calculado</t>
   </si>
   <si>
-    <t>Chat da Lu (IA)</t>
+    <t>Chat da Luna (IA)</t>
   </si>
   <si>
     <t>msgs × (entrada × preço + saída × preço)</t>
@@ -374,6 +395,12 @@
   </si>
   <si>
     <t>idem</t>
+  </si>
+  <si>
+    <t>Rascunho de resposta pra Luciana (IA)</t>
+  </si>
+  <si>
+    <t>dúvidas × (entrada × preço + saída × preço)</t>
   </si>
   <si>
     <t>R2: fotos guardadas</t>
@@ -1037,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1267,420 +1294,462 @@
         <v>40</v>
       </c>
       <c r="B22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5">
-        <v>20000</v>
+        <v>2500</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B27" s="5">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="5">
-        <v>20</v>
-      </c>
-      <c r="C28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B29" s="5">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="5">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
         <v>54</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.0009</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
       </c>
       <c r="D30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>56</v>
+      </c>
+      <c r="B31" s="5">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="5">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B33" s="5">
-        <v>30</v>
+        <v>0.0009</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="5">
-        <v>150</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="5">
-        <v>6</v>
-      </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="D35" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="5">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
         <v>65</v>
-      </c>
-      <c r="B36" s="5">
-        <v>0.015</v>
-      </c>
-      <c r="C36" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="5">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" t="s">
         <v>68</v>
-      </c>
-      <c r="B37" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="5">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
         <v>71</v>
-      </c>
-      <c r="B38" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="5">
+        <v>0.015</v>
+      </c>
+      <c r="C39" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="5">
-        <v>10</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>74</v>
       </c>
-      <c r="D39" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="B40" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="C40" t="s">
         <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B42" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="5">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="C44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B45" s="5">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B46" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>86</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B49" s="5">
+        <v>20</v>
+      </c>
+      <c r="C49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>94</v>
+      </c>
+      <c r="B52" s="5">
         <v>0</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C52" t="s">
         <v>20</v>
       </c>
-      <c r="D49" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>89</v>
-      </c>
-      <c r="B50" s="5">
-        <v>0.008</v>
-      </c>
-      <c r="C50" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>91</v>
+      <c r="D52" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B53" s="5">
-        <v>6</v>
+        <v>0.008</v>
       </c>
       <c r="C53" t="s">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>95</v>
-      </c>
-      <c r="B54" s="5">
-        <v>3</v>
-      </c>
-      <c r="C54" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B55" s="5">
-        <v>2</v>
-      </c>
-      <c r="C55" t="s">
         <v>97</v>
       </c>
-      <c r="D55" t="s">
-        <v>38</v>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B56" s="5">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="5">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>101</v>
+      <c r="D57" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="5">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B59" s="5">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="5">
         <v>0</v>
       </c>
-      <c r="C59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" s="5">
+      <c r="C62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D62" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="5">
         <v>0.099</v>
       </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="5">
+      <c r="C63" t="s">
+        <v>113</v>
+      </c>
+      <c r="D63" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" s="5">
         <v>1</v>
       </c>
-      <c r="C61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C64" t="s">
+        <v>110</v>
+      </c>
+      <c r="D64" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1692,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1702,31 +1771,31 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B5" s="6">
         <f>Premissas!$B$13*(Premissas!$B$14*Premissas!$B$11+Premissas!$B$15*Premissas!$B$12)/1000000</f>
@@ -1737,12 +1806,12 @@
         <v>0.37125</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B6" s="6">
         <f>Premissas!$B$16*(Premissas!$B$17*Premissas!$B$11+Premissas!$B$18*Premissas!$B$12)/1000000</f>
@@ -1753,12 +1822,12 @@
         <v>0.408375</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B7" s="6">
         <f>Premissas!$B$19*(Premissas!$B$20*Premissas!$B$11+Premissas!$B$21*Premissas!$B$12)/1000000</f>
@@ -1769,99 +1838,115 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B8" s="6">
-        <f>(Premissas!$B$33*Premissas!$B$34*Premissas!$B$35/1024/1024)*Premissas!$B$36</f>
-        <v>0.00038623809814453125</v>
+        <f>Premissas!$B$22*(Premissas!$B$23*Premissas!$B$11+Premissas!$B$24*Premissas!$B$12)/1000000</f>
+        <v>0.006</v>
       </c>
       <c r="C8" s="7">
         <f>B8*Premissas!$B$7</f>
-        <v>0.002124309539794922</v>
+        <v>0.033</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B9" s="6">
-        <f>Premissas!$B$33*(Premissas!$B$37+Premissas!$B$39*Premissas!$B$38)/1000000</f>
-        <v>0.000243</v>
+        <f>(Premissas!$B$36*Premissas!$B$37*Premissas!$B$38/1024/1024)*Premissas!$B$39</f>
+        <v>0.00038623809814453125</v>
       </c>
       <c r="C9" s="7">
         <f>B9*Premissas!$B$7</f>
-        <v>0.0013365</v>
+        <v>0.002124309539794922</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B10" s="6">
-        <f>Premissas!$B$27*Premissas!$B$30</f>
-        <v>0.0063</v>
+        <f>Premissas!$B$36*(Premissas!$B$40+Premissas!$B$42*Premissas!$B$41)/1000000</f>
+        <v>0.000243</v>
       </c>
       <c r="C10" s="7">
         <f>B10*Premissas!$B$7</f>
-        <v>0.03465</v>
+        <v>0.0013365</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B11" s="6">
-        <f>Premissas!$B$49*Premissas!$B$50</f>
-        <v>0</v>
+        <f>Premissas!$B$30*Premissas!$B$33</f>
+        <v>0.0063</v>
       </c>
       <c r="C11" s="7">
         <f>B11*Premissas!$B$7</f>
+        <v>0.03465</v>
+      </c>
+      <c r="D11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="6">
+        <f>Premissas!$B$52*Premissas!$B$53</f>
         <v>0</v>
       </c>
-      <c r="D11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="9">
-        <f>'Por paciente'!$B$5+'Por paciente'!$B$6+'Por paciente'!$B$7+'Por paciente'!$B$8+'Por paciente'!$B$9+'Por paciente'!$B$11</f>
-        <v>0.1423792380981445</v>
-      </c>
-      <c r="C13" s="10">
-        <f>B13*Premissas!$B$7</f>
-        <v>0.7830858095397948</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>129</v>
+      <c r="C12" s="7">
+        <f>B12*Premissas!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="9">
+        <f>'Por paciente'!$B$5+'Por paciente'!$B$6+'Por paciente'!$B$7+'Por paciente'!$B$8+'Por paciente'!$B$9+'Por paciente'!$B$10+'Por paciente'!$B$12</f>
+        <v>0.14837923809814452</v>
+      </c>
+      <c r="C14" s="10">
+        <f>B14*Premissas!$B$7</f>
+        <v>0.8160858095397948</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>130</v>
+      <c r="A16" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1882,37 +1967,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B5" s="11">
         <v>1000</v>
@@ -1927,70 +2012,70 @@
         <v>30000</v>
       </c>
       <c r="F5" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B8" s="12">
-        <f>B$5*'Por paciente'!$B$13</f>
-        <v>142.3792380981445</v>
+        <f>B$5*'Por paciente'!$B$14</f>
+        <v>148.37923809814453</v>
       </c>
       <c r="C8" s="12">
-        <f>C$5*'Por paciente'!$B$13</f>
-        <v>711.8961904907226</v>
+        <f>C$5*'Por paciente'!$B$14</f>
+        <v>741.8961904907226</v>
       </c>
       <c r="D8" s="12">
-        <f>D$5*'Por paciente'!$B$13</f>
-        <v>1423.7923809814451</v>
+        <f>D$5*'Por paciente'!$B$14</f>
+        <v>1483.7923809814451</v>
       </c>
       <c r="E8" s="12">
-        <f>E$5*'Por paciente'!$B$13</f>
-        <v>4271.377142944335</v>
+        <f>E$5*'Por paciente'!$B$14</f>
+        <v>4451.377142944336</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B11" s="12">
-        <f>IF(B$5*Premissas!$B$27&lt;=3000,0,IF(B$5*Premissas!$B$27&lt;=50000,Premissas!$B$28,IF(B$5*Premissas!$B$27&lt;=100000,Premissas!$B$29,Premissas!$B$29+(B$5*Premissas!$B$27-100000)*Premissas!$B$30)))</f>
+        <f>IF(B$5*Premissas!$B$30&lt;=3000,0,IF(B$5*Premissas!$B$30&lt;=50000,Premissas!$B$31,IF(B$5*Premissas!$B$30&lt;=100000,Premissas!$B$32,Premissas!$B$32+(B$5*Premissas!$B$30-100000)*Premissas!$B$33)))</f>
         <v>20</v>
       </c>
       <c r="C11" s="12">
-        <f>IF(C$5*Premissas!$B$27&lt;=3000,0,IF(C$5*Premissas!$B$27&lt;=50000,Premissas!$B$28,IF(C$5*Premissas!$B$27&lt;=100000,Premissas!$B$29,Premissas!$B$29+(C$5*Premissas!$B$27-100000)*Premissas!$B$30)))</f>
+        <f>IF(C$5*Premissas!$B$30&lt;=3000,0,IF(C$5*Premissas!$B$30&lt;=50000,Premissas!$B$31,IF(C$5*Premissas!$B$30&lt;=100000,Premissas!$B$32,Premissas!$B$32+(C$5*Premissas!$B$30-100000)*Premissas!$B$33)))</f>
         <v>20</v>
       </c>
       <c r="D11" s="12">
-        <f>IF(D$5*Premissas!$B$27&lt;=3000,0,IF(D$5*Premissas!$B$27&lt;=50000,Premissas!$B$28,IF(D$5*Premissas!$B$27&lt;=100000,Premissas!$B$29,Premissas!$B$29+(D$5*Premissas!$B$27-100000)*Premissas!$B$30)))</f>
+        <f>IF(D$5*Premissas!$B$30&lt;=3000,0,IF(D$5*Premissas!$B$30&lt;=50000,Premissas!$B$31,IF(D$5*Premissas!$B$30&lt;=100000,Premissas!$B$32,Premissas!$B$32+(D$5*Premissas!$B$30-100000)*Premissas!$B$33)))</f>
         <v>90</v>
       </c>
       <c r="E11" s="12">
-        <f>IF(E$5*Premissas!$B$27&lt;=3000,0,IF(E$5*Premissas!$B$27&lt;=50000,Premissas!$B$28,IF(E$5*Premissas!$B$27&lt;=100000,Premissas!$B$29,Premissas!$B$29+(E$5*Premissas!$B$27-100000)*Premissas!$B$30)))</f>
+        <f>IF(E$5*Premissas!$B$30&lt;=3000,0,IF(E$5*Premissas!$B$30&lt;=50000,Premissas!$B$31,IF(E$5*Premissas!$B$30&lt;=100000,Premissas!$B$32,Premissas!$B$32+(E$5*Premissas!$B$30-100000)*Premissas!$B$33)))</f>
         <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B12" s="13">
         <v>1</v>
@@ -2005,12 +2090,12 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B13" s="13">
         <v>1</v>
@@ -2025,12 +2110,12 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B14" s="13">
         <v>1</v>
@@ -2045,12 +2130,12 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B15" s="13">
         <v>2</v>
@@ -2065,12 +2150,12 @@
         <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B16" s="13">
         <v>5</v>
@@ -2085,12 +2170,12 @@
         <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B17" s="13">
         <v>30</v>
@@ -2105,60 +2190,60 @@
         <v>700</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B18" s="12">
-        <f>Premissas!$B$46+(B12+B14)*Premissas!$B$42+(B13+B15)*Premissas!$B$43+B16*Premissas!$B$44+B17*Premissas!$B$45</f>
+        <f>Premissas!$B$49+(B12+B14)*Premissas!$B$45+(B13+B15)*Premissas!$B$46+B16*Premissas!$B$47+B17*Premissas!$B$48</f>
         <v>92.25</v>
       </c>
       <c r="C18" s="12">
-        <f>Premissas!$B$46+(C12+C14)*Premissas!$B$42+(C13+C15)*Premissas!$B$43+C16*Premissas!$B$44+C17*Premissas!$B$45</f>
+        <f>Premissas!$B$49+(C12+C14)*Premissas!$B$45+(C13+C15)*Premissas!$B$46+C16*Premissas!$B$47+C17*Premissas!$B$48</f>
         <v>168.25</v>
       </c>
       <c r="D18" s="12">
-        <f>Premissas!$B$46+(D12+D14)*Premissas!$B$42+(D13+D15)*Premissas!$B$43+D16*Premissas!$B$44+D17*Premissas!$B$45</f>
+        <f>Premissas!$B$49+(D12+D14)*Premissas!$B$45+(D13+D15)*Premissas!$B$46+D16*Premissas!$B$47+D17*Premissas!$B$48</f>
         <v>237</v>
       </c>
       <c r="E18" s="12">
-        <f>Premissas!$B$46+(E12+E14)*Premissas!$B$42+(E13+E15)*Premissas!$B$43+E16*Premissas!$B$44+E17*Premissas!$B$45</f>
+        <f>Premissas!$B$49+(E12+E14)*Premissas!$B$45+(E13+E15)*Premissas!$B$46+E16*Premissas!$B$47+E17*Premissas!$B$48</f>
         <v>467</v>
       </c>
       <c r="F18" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B19" s="12">
-        <f>Premissas!$B$22*30*(Premissas!$B$23*Premissas!$B$11+Premissas!$B$24*Premissas!$B$12)/1000000</f>
+        <f>Premissas!$B$25*30*(Premissas!$B$26*Premissas!$B$11+Premissas!$B$27*Premissas!$B$12)/1000000</f>
         <v>0.585</v>
       </c>
       <c r="C19" s="12">
-        <f>Premissas!$B$22*30*(Premissas!$B$23*Premissas!$B$11+Premissas!$B$24*Premissas!$B$12)/1000000</f>
+        <f>Premissas!$B$25*30*(Premissas!$B$26*Premissas!$B$11+Premissas!$B$27*Premissas!$B$12)/1000000</f>
         <v>0.585</v>
       </c>
       <c r="D19" s="12">
-        <f>Premissas!$B$22*30*(Premissas!$B$23*Premissas!$B$11+Premissas!$B$24*Premissas!$B$12)/1000000</f>
+        <f>Premissas!$B$25*30*(Premissas!$B$26*Premissas!$B$11+Premissas!$B$27*Premissas!$B$12)/1000000</f>
         <v>0.585</v>
       </c>
       <c r="E19" s="12">
-        <f>Premissas!$B$22*30*(Premissas!$B$23*Premissas!$B$11+Premissas!$B$24*Premissas!$B$12)/1000000</f>
+        <f>Premissas!$B$25*30*(Premissas!$B$26*Premissas!$B$11+Premissas!$B$27*Premissas!$B$12)/1000000</f>
         <v>0.585</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B20" s="12">
         <v>0</v>
@@ -2173,185 +2258,185 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B22" s="14">
         <f>B8+B11+B18+B19+B20</f>
-        <v>255.2142380981445</v>
+        <v>261.2142380981445</v>
       </c>
       <c r="C22" s="14">
         <f>C8+C11+C18+C19+C20</f>
-        <v>900.7311904907226</v>
+        <v>930.7311904907226</v>
       </c>
       <c r="D22" s="14">
         <f>D8+D11+D18+D19+D20</f>
-        <v>1751.3773809814452</v>
+        <v>1811.3773809814452</v>
       </c>
       <c r="E22" s="14">
         <f>E8+E11+E18+E19+E20</f>
-        <v>4927.962142944335</v>
+        <v>5107.962142944336</v>
       </c>
       <c r="F22" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B23" s="14">
         <f>B22*Premissas!$B$7</f>
-        <v>1403.6783095397948</v>
+        <v>1436.6783095397948</v>
       </c>
       <c r="C23" s="14">
         <f>C22*Premissas!$B$7</f>
-        <v>4954.021547698974</v>
+        <v>5119.021547698974</v>
       </c>
       <c r="D23" s="14">
         <f>D22*Premissas!$B$7</f>
-        <v>9632.575595397948</v>
+        <v>9962.575595397948</v>
       </c>
       <c r="E23" s="14">
         <f>E22*Premissas!$B$7</f>
-        <v>27103.791786193844</v>
+        <v>28093.791786193848</v>
       </c>
       <c r="F23" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B24" s="14">
         <f>B23/B$5</f>
-        <v>1.4036783095397949</v>
+        <v>1.4366783095397948</v>
       </c>
       <c r="C24" s="14">
         <f>C23/C$5</f>
-        <v>0.9908043095397948</v>
+        <v>1.0238043095397948</v>
       </c>
       <c r="D24" s="14">
         <f>D23/D$5</f>
-        <v>0.9632575595397947</v>
+        <v>0.9962575595397948</v>
       </c>
       <c r="E24" s="14">
         <f>E23/E$5</f>
-        <v>0.9034597262064614</v>
+        <v>0.9364597262064616</v>
       </c>
       <c r="F24" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B27" s="13">
-        <f>(B$5*Premissas!$B$53+B$5*Premissas!$B$55*Premissas!$B$54)/60</f>
+        <f>(B$5*Premissas!$B$56+B$5*Premissas!$B$58*Premissas!$B$57)/60</f>
         <v>200</v>
       </c>
       <c r="C27" s="13">
-        <f>(C$5*Premissas!$B$53+C$5*Premissas!$B$55*Premissas!$B$54)/60</f>
+        <f>(C$5*Premissas!$B$56+C$5*Premissas!$B$58*Premissas!$B$57)/60</f>
         <v>1000</v>
       </c>
       <c r="D27" s="13">
-        <f>(D$5*Premissas!$B$53+D$5*Premissas!$B$55*Premissas!$B$54)/60</f>
+        <f>(D$5*Premissas!$B$56+D$5*Premissas!$B$58*Premissas!$B$57)/60</f>
         <v>2000</v>
       </c>
       <c r="E27" s="13">
-        <f>(E$5*Premissas!$B$53+E$5*Premissas!$B$55*Premissas!$B$54)/60</f>
+        <f>(E$5*Premissas!$B$56+E$5*Premissas!$B$58*Premissas!$B$57)/60</f>
         <v>6000</v>
       </c>
       <c r="F27" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B28" s="15">
-        <f>B27/Premissas!$B$56</f>
+        <f>B27/Premissas!$B$59</f>
         <v>1.4285714285714286</v>
       </c>
       <c r="C28" s="15">
-        <f>C27/Premissas!$B$56</f>
+        <f>C27/Premissas!$B$59</f>
         <v>7.142857142857143</v>
       </c>
       <c r="D28" s="15">
-        <f>D27/Premissas!$B$56</f>
+        <f>D27/Premissas!$B$59</f>
         <v>14.285714285714286</v>
       </c>
       <c r="E28" s="15">
-        <f>E27/Premissas!$B$56</f>
+        <f>E27/Premissas!$B$59</f>
         <v>42.857142857142854</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B31" s="12">
-        <f>IF(Premissas!$B$59&gt;0,B$5*(Premissas!$B$59*(1-Premissas!$B$60)-Premissas!$B$61),0)</f>
+        <f>IF(Premissas!$B$62&gt;0,B$5*(Premissas!$B$62*(1-Premissas!$B$63)-Premissas!$B$64),0)</f>
         <v>0</v>
       </c>
       <c r="C31" s="12">
-        <f>IF(Premissas!$B$59&gt;0,C$5*(Premissas!$B$59*(1-Premissas!$B$60)-Premissas!$B$61),0)</f>
+        <f>IF(Premissas!$B$62&gt;0,C$5*(Premissas!$B$62*(1-Premissas!$B$63)-Premissas!$B$64),0)</f>
         <v>0</v>
       </c>
       <c r="D31" s="12">
-        <f>IF(Premissas!$B$59&gt;0,D$5*(Premissas!$B$59*(1-Premissas!$B$60)-Premissas!$B$61),0)</f>
+        <f>IF(Premissas!$B$62&gt;0,D$5*(Premissas!$B$62*(1-Premissas!$B$63)-Premissas!$B$64),0)</f>
         <v>0</v>
       </c>
       <c r="E31" s="12">
-        <f>IF(Premissas!$B$59&gt;0,E$5*(Premissas!$B$59*(1-Premissas!$B$60)-Premissas!$B$61),0)</f>
+        <f>IF(Premissas!$B$62&gt;0,E$5*(Premissas!$B$62*(1-Premissas!$B$63)-Premissas!$B$64),0)</f>
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B32" s="12">
-        <f>IF(Premissas!$B$59&gt;0,B31-B23,0)</f>
+        <f>IF(Premissas!$B$62&gt;0,B31-B23,0)</f>
         <v>0</v>
       </c>
       <c r="C32" s="12">
-        <f>IF(Premissas!$B$59&gt;0,C31-C23,0)</f>
+        <f>IF(Premissas!$B$62&gt;0,C31-C23,0)</f>
         <v>0</v>
       </c>
       <c r="D32" s="12">
-        <f>IF(Premissas!$B$59&gt;0,D31-D23,0)</f>
+        <f>IF(Premissas!$B$62&gt;0,D31-D23,0)</f>
         <v>0</v>
       </c>
       <c r="E32" s="12">
-        <f>IF(Premissas!$B$59&gt;0,E31-E23,0)</f>
+        <f>IF(Premissas!$B$62&gt;0,E31-E23,0)</f>
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2371,103 +2456,103 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
